--- a/artfynd/A 31438-2024 artfynd.xlsx
+++ b/artfynd/A 31438-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123324335</v>
       </c>
       <c r="B2" t="n">
-        <v>98282</v>
+        <v>98285</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31438-2024 artfynd.xlsx
+++ b/artfynd/A 31438-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123324335</v>
       </c>
       <c r="B2" t="n">
-        <v>98285</v>
+        <v>98287</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31438-2024 artfynd.xlsx
+++ b/artfynd/A 31438-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123324335</v>
       </c>
       <c r="B2" t="n">
-        <v>98287</v>
+        <v>98293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31438-2024 artfynd.xlsx
+++ b/artfynd/A 31438-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123324335</v>
       </c>
       <c r="B2" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31438-2024 artfynd.xlsx
+++ b/artfynd/A 31438-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123324335</v>
       </c>
       <c r="B2" t="n">
-        <v>98296</v>
+        <v>98313</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31438-2024 artfynd.xlsx
+++ b/artfynd/A 31438-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123324335</v>
       </c>
       <c r="B2" t="n">
-        <v>98313</v>
+        <v>98419</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31438-2024 artfynd.xlsx
+++ b/artfynd/A 31438-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123324335</v>
       </c>
       <c r="B2" t="n">
-        <v>98419</v>
+        <v>98421</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31438-2024 artfynd.xlsx
+++ b/artfynd/A 31438-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123324335</v>
       </c>
       <c r="B2" t="n">
-        <v>98421</v>
+        <v>97996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
